--- a/UOL_Separated_All_Activity_Data_Cleaned.xlsx
+++ b/UOL_Separated_All_Activity_Data_Cleaned.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Job UOL Work\UOL Dashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4776C6E4-00FE-4F92-AB83-100428AC90B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E48C049F-C062-48CA-8132-A6471956A60B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-90" windowWidth="29040" windowHeight="15720" firstSheet="12" activeTab="18" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-90" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>

--- a/UOL_Separated_All_Activity_Data_Cleaned.xlsx
+++ b/UOL_Separated_All_Activity_Data_Cleaned.xlsx
@@ -2,35 +2,35 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R0c58bcb6b34048e6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All Separated Activities" sheetId="2" r:id="R8b6373e6feb24d40"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Alumni Talk - Mentoring" sheetId="3" r:id="R9a7bdbfb3e734673"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Community Engagement" sheetId="4" r:id="R09bc3854be64413c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Conference" sheetId="5" r:id="Rba5a5e39611047e6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Curriculum Feedback Session" sheetId="6" r:id="R8884e0e2aa0c48f1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GLIT" sheetId="7" r:id="R023c4dacb98d4b71"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guest Lecture" sheetId="8" r:id="Rbcee8ab9156548be"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IAB Meeting - Industry Consulta" sheetId="9" r:id="Rf79250df3988410f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IP" sheetId="10" r:id="R53d076185dec4c6d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IV" sheetId="11" r:id="R53aa8f0767394940"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Industrial Visit" sheetId="12" r:id="R974e6294a1b043c6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Internship-Placement" sheetId="13" r:id="R4f0c77b98549429c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MOU" sheetId="14" r:id="R458dc294c58247a6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MoU Signing (Memorandum of Unde" sheetId="15" r:id="R3a652f5ef613428c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Others" sheetId="16" r:id="R5d5ae77d1d154701"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Research Collaboration" sheetId="17" r:id="Rb3b5f38aa90e4787"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Seminar" sheetId="18" r:id="R07555fbaa74e4ea0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unclassified" sheetId="19" r:id="R6509a6b99a634ce1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Workshop" sheetId="20" r:id="Rb5713055d8f04258"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guest Lecture - GLIT" sheetId="21" r:id="R12dd0b22f0dc461f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Industrial Visit - IV" sheetId="22" r:id="R43cd131aa5da4c26"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Internship - Placement" sheetId="23" r:id="Rc61fca62683e4c40"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MoU - MoU Signing" sheetId="24" r:id="Rb4d33ff4bc9a48e3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="New Data Added" sheetId="25" r:id="R00a58db3d7854321"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Planned - Section 4" sheetId="26" r:id="Rabfb1e31dd4241c1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Planned Activities" sheetId="27" r:id="Rf52ff2497fcf4119"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remote Activities" sheetId="28" r:id="Rade993eb4b034e58"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="64 Submission Reconciliation" sheetId="29" r:id="R55a5037ce846417a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R94aaebbc22d54368"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All Separated Activities" sheetId="2" r:id="Raa0f83892ce94080"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Alumni Talk - Mentoring" sheetId="3" r:id="R3a6ad58a82e9489f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Community Engagement" sheetId="4" r:id="R5acb60b1b4ce4564"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Conference" sheetId="5" r:id="Rd0f2d5ce70d64d63"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Curriculum Feedback Session" sheetId="6" r:id="Rf961273c42004a88"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GLIT" sheetId="7" r:id="R76d2ecb11cf14d24"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guest Lecture" sheetId="8" r:id="R73dc25f5d68d4ce5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IAB Meeting - Industry Consulta" sheetId="9" r:id="Rabd1edcc6edf4d7f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IP" sheetId="10" r:id="R2aae2da38527497e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IV" sheetId="11" r:id="R74c191dc67134cd2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Industrial Visit" sheetId="12" r:id="R453c826e4231456e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Internship-Placement" sheetId="13" r:id="R8a687fc1512d4881"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MOU" sheetId="14" r:id="R711a54d532e94fe9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MoU Signing (Memorandum of Unde" sheetId="15" r:id="Rc9e004a4358c42fb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Others" sheetId="16" r:id="Rca893c5ca00647fe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Research Collaboration" sheetId="17" r:id="R6875537773a34da1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Seminar" sheetId="18" r:id="R0480cb129cbc474b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unclassified" sheetId="19" r:id="Rf8b516e3a4004080"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Workshop" sheetId="20" r:id="Reaa51435b7024e26"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guest Lecture - GLIT" sheetId="21" r:id="R8986ad3d2e114001"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Industrial Visit - IV" sheetId="22" r:id="Raf8a795aabca4391"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Internship - Placement" sheetId="23" r:id="Rc9cb3d36cb794bfe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MoU - MoU Signing" sheetId="24" r:id="Rb4dcea764dad431e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="New Data Added" sheetId="25" r:id="R3a6f16dbc2d34bb3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Planned - Section 4" sheetId="26" r:id="R0d0bb2f33dbb4ee7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Planned Activities" sheetId="27" r:id="Rd34f71a9b5524bde"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remote Activities" sheetId="28" r:id="R1e5a3d99aa0346d6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="64 Submission Reconciliation" sheetId="29" r:id="R2c8e779574ff4cd4"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18596,7 +18596,7 @@
       <x:c r="L75" s="2" t="str">
         <x:v>Alumni Talk / Mentoring</x:v>
       </x:c>
-      <x:c r="M75" s="2" t="str">
+      <x:c r="M75" s="2" t="n">
         <x:v>590</x:v>
       </x:c>
       <x:c r="N75" s="2" t="str">
@@ -47824,7 +47824,7 @@
       <x:c r="L2" s="2" t="str">
         <x:v>Alumni Talk / Mentoring</x:v>
       </x:c>
-      <x:c r="M2" s="2" t="str">
+      <x:c r="M2" s="2" t="n">
         <x:v>590</x:v>
       </x:c>
       <x:c r="N2" s="2" t="str">
